--- a/separationIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
+++ b/separationIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T08:46:53+00:00</t>
+    <t>2026-09-25T09:30:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/separationIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
+++ b/separationIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T09:30:48+00:00</t>
+    <t>2026-09-28T09:51:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/separationIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
+++ b/separationIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T09:51:12+00:00</t>
+    <t>2026-09-28T15:08:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/separationIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
+++ b/separationIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T15:08:08+00:00</t>
+    <t>2026-09-28T15:35:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/separationIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
+++ b/separationIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T15:35:27+00:00</t>
+    <t>2026-09-28T21:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/separationIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
+++ b/separationIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T21:40:58+00:00</t>
+    <t>2026-09-29T08:04:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
